--- a/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
+++ b/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
@@ -1581,9 +1581,8 @@
     <col min="21" max="21" width="12.375" style="1" customWidth="1"/>
     <col min="22" max="22" width="13.375" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.8833333333333" style="1" customWidth="1"/>
-    <col min="24" max="24" width="24.5" style="1" customWidth="1"/>
-    <col min="25" max="25" width="28.5" style="1" customWidth="1"/>
-    <col min="26" max="27" width="8.38333333333333" style="1" customWidth="1"/>
+    <col min="24" max="26" width="9.875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="35.875" style="1" customWidth="1"/>
     <col min="28" max="28" width="7.88333333333333" style="1" customWidth="1"/>
     <col min="29" max="29" width="28" style="1" customWidth="1"/>
   </cols>

--- a/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
+++ b/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="107">
   <si>
     <t>##var</t>
   </si>
@@ -197,7 +197,7 @@
     <t>0,98</t>
   </si>
   <si>
-    <t>250</t>
+    <t>500</t>
   </si>
   <si>
     <t>双侧</t>
@@ -218,7 +218,7 @@
     <t>-66,-12</t>
   </si>
   <si>
-    <t>220</t>
+    <t>450</t>
   </si>
   <si>
     <t>左侧</t>
@@ -242,13 +242,16 @@
     <t>-60,-14</t>
   </si>
   <si>
-    <t>180</t>
+    <t>400</t>
   </si>
   <si>
     <t>60,-14</t>
   </si>
   <si>
-    <t>0,20</t>
+    <t>0,110</t>
+  </si>
+  <si>
+    <t>350</t>
   </si>
   <si>
     <t>aircraft/self/player_aircraft_heavy_001_lv01</t>
@@ -1043,7 +1046,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1069,9 +1072,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1573,14 +1573,15 @@
     <col min="12" max="12" width="13.1333333333333" style="1" customWidth="1"/>
     <col min="13" max="13" width="7" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.625" style="1" customWidth="1"/>
-    <col min="15" max="16" width="10.8833333333333" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="12.375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="13.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.8833333333333" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.25" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="12.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13.375" style="1" customWidth="1"/>
     <col min="24" max="26" width="9.875" style="1" customWidth="1"/>
     <col min="27" max="27" width="35.875" style="1" customWidth="1"/>
     <col min="28" max="28" width="7.88333333333333" style="1" customWidth="1"/>
@@ -1916,7 +1917,7 @@
         <v>55</v>
       </c>
       <c r="P7" s="4">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="Q7" s="4">
         <v>1</v>
@@ -1993,7 +1994,7 @@
         <v>62</v>
       </c>
       <c r="P8" s="4">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="Q8" s="4">
         <v>1</v>
@@ -2048,7 +2049,7 @@
         <v>65</v>
       </c>
       <c r="P9" s="4">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="Q9" s="4">
         <v>1</v>
@@ -2056,7 +2057,7 @@
       <c r="R9" s="4">
         <v>3</v>
       </c>
-      <c r="S9" s="17" t="s">
+      <c r="S9" s="6" t="s">
         <v>63</v>
       </c>
       <c r="T9" s="4">
@@ -2117,7 +2118,7 @@
         <v>70</v>
       </c>
       <c r="P10" s="4">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="Q10" s="4">
         <v>1</v>
@@ -2125,7 +2126,7 @@
       <c r="R10" s="4">
         <v>4</v>
       </c>
-      <c r="S10" s="17" t="s">
+      <c r="S10" s="16" t="s">
         <v>71</v>
       </c>
       <c r="T10" s="4">
@@ -2167,12 +2168,12 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="12"/>
-      <c r="N11" s="13"/>
+      <c r="N11" s="6"/>
       <c r="O11" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P11" s="4">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="Q11" s="4">
         <v>1</v>
@@ -2180,7 +2181,7 @@
       <c r="R11" s="4">
         <v>4</v>
       </c>
-      <c r="S11" s="17" t="s">
+      <c r="S11" s="16" t="s">
         <v>71</v>
       </c>
       <c r="T11" s="4">
@@ -2209,17 +2210,17 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="14"/>
+      <c r="I12" s="13"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="16"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="15"/>
       <c r="O12" s="6" t="s">
         <v>73</v>
       </c>
       <c r="P12" s="4">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="Q12" s="4">
         <v>1</v>
@@ -2227,18 +2228,18 @@
       <c r="R12" s="4">
         <v>1</v>
       </c>
-      <c r="S12" s="6">
-        <v>900</v>
+      <c r="S12" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="W12" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -2266,24 +2267,24 @@
         <v>1250</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M13" s="4">
         <v>150</v>
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P13" s="4">
         <v>1001</v>
@@ -2341,24 +2342,24 @@
         <v>1550</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M14" s="4">
         <v>190</v>
       </c>
       <c r="N14" s="6"/>
       <c r="O14" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P14" s="4">
         <v>1001</v>
@@ -2416,24 +2417,24 @@
         <v>1900</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M15" s="4">
         <v>240</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P15" s="4">
         <v>1001</v>
@@ -2491,24 +2492,24 @@
         <v>900</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M16" s="4">
         <v>80</v>
       </c>
       <c r="N16" s="6"/>
       <c r="O16" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P16" s="4">
         <v>1001</v>
@@ -2566,24 +2567,24 @@
         <v>1100</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M17" s="4">
         <v>95</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P17" s="4">
         <v>1001</v>
@@ -2641,24 +2642,24 @@
         <v>1350</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M18" s="4">
         <v>115</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="4">
         <v>1001</v>
@@ -2716,24 +2717,24 @@
         <v>1650</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M19" s="4">
         <v>140</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="4">
         <v>1001</v>
@@ -2791,24 +2792,24 @@
         <v>1100</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M20" s="4">
         <v>90</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="4">
         <v>1001</v>
@@ -2866,24 +2867,24 @@
         <v>1350</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M21" s="4">
         <v>110</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="4">
         <v>1001</v>
@@ -2941,24 +2942,24 @@
         <v>1650</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M22" s="4">
         <v>135</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P22" s="4">
         <v>1001</v>
@@ -3016,24 +3017,24 @@
         <v>2000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M23" s="4">
         <v>165</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P23" s="4">
         <v>1001</v>
@@ -3091,24 +3092,24 @@
         <v>1350</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M24" s="4">
         <v>95</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P24" s="4">
         <v>1001</v>
@@ -3166,24 +3167,24 @@
         <v>1650</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M25" s="4">
         <v>115</v>
       </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P25" s="4">
         <v>1001</v>
@@ -3241,24 +3242,24 @@
         <v>2000</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M26" s="4">
         <v>145</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P26" s="4">
         <v>1001</v>
@@ -3316,24 +3317,24 @@
         <v>2400</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M27" s="4">
         <v>180</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P27" s="4">
         <v>1001</v>

--- a/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
+++ b/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -50,7 +50,7 @@
     <t>basePower</t>
   </si>
   <si>
-    <t>aircraft</t>
+    <t>unit</t>
   </si>
   <si>
     <t>##</t>
@@ -74,7 +74,7 @@
     <t>基础战力</t>
   </si>
   <si>
-    <t>飞机实体</t>
+    <t>飞行单位</t>
   </si>
   <si>
     <t>##type</t>
@@ -86,7 +86,7 @@
     <t>vector2</t>
   </si>
   <si>
-    <t>Aircraft</t>
+    <t>FlyingUnit</t>
   </si>
   <si>
     <t>appearanceName</t>
@@ -218,9 +218,6 @@
     <t>-66,-12</t>
   </si>
   <si>
-    <t>450</t>
-  </si>
-  <si>
     <t>左侧</t>
   </si>
   <si>
@@ -242,7 +239,7 @@
     <t>-60,-14</t>
   </si>
   <si>
-    <t>400</t>
+    <t>250</t>
   </si>
   <si>
     <t>60,-14</t>
@@ -251,7 +248,7 @@
     <t>0,110</t>
   </si>
   <si>
-    <t>350</t>
+    <t>190</t>
   </si>
   <si>
     <t>aircraft/self/player_aircraft_heavy_001_lv01</t>
@@ -1923,13 +1920,13 @@
         <v>1</v>
       </c>
       <c r="R7" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>56</v>
       </c>
       <c r="T7" s="4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="U7" s="4">
         <v>90</v>
@@ -2000,22 +1997,22 @@
         <v>1</v>
       </c>
       <c r="R8" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="T8" s="4">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="U8" s="4">
         <v>90</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W8" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" s="4">
         <v>0</v>
@@ -2046,7 +2043,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P9" s="4">
         <v>1003</v>
@@ -2055,22 +2052,22 @@
         <v>1</v>
       </c>
       <c r="R9" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="T9" s="4">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="U9" s="4">
         <v>90</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W9" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -2098,24 +2095,24 @@
         <v>1550</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="M10" s="4">
         <v>150</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P10" s="4">
         <v>1003</v>
@@ -2124,10 +2121,10 @@
         <v>1</v>
       </c>
       <c r="R10" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T10" s="4">
         <v>40</v>
@@ -2136,7 +2133,7 @@
         <v>90</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W10" s="4">
         <v>2</v>
@@ -2170,7 +2167,7 @@
       <c r="M11" s="12"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" s="4">
         <v>1003</v>
@@ -2179,10 +2176,10 @@
         <v>1</v>
       </c>
       <c r="R11" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S11" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T11" s="4">
         <v>40</v>
@@ -2191,7 +2188,7 @@
         <v>90</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W11" s="4">
         <v>2</v>
@@ -2217,7 +2214,7 @@
       <c r="M12" s="14"/>
       <c r="N12" s="15"/>
       <c r="O12" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P12" s="4">
         <v>1001</v>
@@ -2226,12 +2223,14 @@
         <v>1</v>
       </c>
       <c r="R12" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="T12" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="T12" s="4">
+        <v>50</v>
+      </c>
       <c r="U12" s="4">
         <v>90</v>
       </c>
@@ -2267,24 +2266,24 @@
         <v>1250</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="M13" s="4">
         <v>150</v>
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P13" s="4">
         <v>1001</v>
@@ -2342,24 +2341,24 @@
         <v>1550</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M14" s="4">
         <v>190</v>
       </c>
       <c r="N14" s="6"/>
       <c r="O14" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P14" s="4">
         <v>1001</v>
@@ -2417,24 +2416,24 @@
         <v>1900</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M15" s="4">
         <v>240</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P15" s="4">
         <v>1001</v>
@@ -2492,24 +2491,24 @@
         <v>900</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M16" s="4">
         <v>80</v>
       </c>
       <c r="N16" s="6"/>
       <c r="O16" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P16" s="4">
         <v>1001</v>
@@ -2567,24 +2566,24 @@
         <v>1100</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M17" s="4">
         <v>95</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P17" s="4">
         <v>1001</v>
@@ -2642,24 +2641,24 @@
         <v>1350</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M18" s="4">
         <v>115</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P18" s="4">
         <v>1001</v>
@@ -2717,24 +2716,24 @@
         <v>1650</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M19" s="4">
         <v>140</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P19" s="4">
         <v>1001</v>
@@ -2792,24 +2791,24 @@
         <v>1100</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M20" s="4">
         <v>90</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P20" s="4">
         <v>1001</v>
@@ -2867,24 +2866,24 @@
         <v>1350</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M21" s="4">
         <v>110</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P21" s="4">
         <v>1001</v>
@@ -2942,24 +2941,24 @@
         <v>1650</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M22" s="4">
         <v>135</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P22" s="4">
         <v>1001</v>
@@ -3017,24 +3016,24 @@
         <v>2000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M23" s="4">
         <v>165</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P23" s="4">
         <v>1001</v>
@@ -3092,24 +3091,24 @@
         <v>1350</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M24" s="4">
         <v>95</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P24" s="4">
         <v>1001</v>
@@ -3167,24 +3166,24 @@
         <v>1650</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M25" s="4">
         <v>115</v>
       </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P25" s="4">
         <v>1001</v>
@@ -3242,24 +3241,24 @@
         <v>2000</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M26" s="4">
         <v>145</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P26" s="4">
         <v>1001</v>
@@ -3317,24 +3316,24 @@
         <v>2400</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M27" s="4">
         <v>180</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P27" s="4">
         <v>1001</v>

--- a/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
+++ b/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="107">
   <si>
     <t>##var</t>
   </si>
@@ -197,25 +197,28 @@
     <t>0,98</t>
   </si>
   <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>双侧</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>aircraft/self/player_aircraft_assault_001_lv02</t>
+  </si>
+  <si>
+    <t>50,120</t>
+  </si>
+  <si>
+    <t>0.5,0.63</t>
+  </si>
+  <si>
+    <t>-66,-12</t>
+  </si>
+  <si>
     <t>500</t>
-  </si>
-  <si>
-    <t>双侧</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>aircraft/self/player_aircraft_assault_001_lv02</t>
-  </si>
-  <si>
-    <t>50,120</t>
-  </si>
-  <si>
-    <t>0.5,0.63</t>
-  </si>
-  <si>
-    <t>-66,-12</t>
   </si>
   <si>
     <t>左侧</t>
@@ -2000,7 +2003,7 @@
         <v>8</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="T8" s="4">
         <v>45</v>
@@ -2009,7 +2012,7 @@
         <v>90</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W8" s="4">
         <v>2</v>
@@ -2043,7 +2046,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="6"/>
       <c r="O9" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P9" s="4">
         <v>1003</v>
@@ -2055,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="T9" s="4">
         <v>45</v>
@@ -2064,7 +2067,7 @@
         <v>90</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W9" s="4">
         <v>2</v>
@@ -2095,24 +2098,24 @@
         <v>1550</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M10" s="4">
         <v>150</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P10" s="4">
         <v>1003</v>
@@ -2124,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="S10" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T10" s="4">
         <v>40</v>
@@ -2133,7 +2136,7 @@
         <v>90</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W10" s="4">
         <v>2</v>
@@ -2167,7 +2170,7 @@
       <c r="M11" s="12"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P11" s="4">
         <v>1003</v>
@@ -2179,7 +2182,7 @@
         <v>10</v>
       </c>
       <c r="S11" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T11" s="4">
         <v>40</v>
@@ -2188,7 +2191,7 @@
         <v>90</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W11" s="4">
         <v>2</v>
@@ -2214,7 +2217,7 @@
       <c r="M12" s="14"/>
       <c r="N12" s="15"/>
       <c r="O12" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P12" s="4">
         <v>1001</v>
@@ -2226,7 +2229,7 @@
         <v>3</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T12" s="4">
         <v>50</v>
@@ -2266,24 +2269,24 @@
         <v>1250</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M13" s="4">
         <v>150</v>
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P13" s="4">
         <v>1001</v>
@@ -2341,24 +2344,24 @@
         <v>1550</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M14" s="4">
         <v>190</v>
       </c>
       <c r="N14" s="6"/>
       <c r="O14" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P14" s="4">
         <v>1001</v>
@@ -2416,24 +2419,24 @@
         <v>1900</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M15" s="4">
         <v>240</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P15" s="4">
         <v>1001</v>
@@ -2491,24 +2494,24 @@
         <v>900</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M16" s="4">
         <v>80</v>
       </c>
       <c r="N16" s="6"/>
       <c r="O16" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P16" s="4">
         <v>1001</v>
@@ -2566,24 +2569,24 @@
         <v>1100</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M17" s="4">
         <v>95</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P17" s="4">
         <v>1001</v>
@@ -2641,24 +2644,24 @@
         <v>1350</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M18" s="4">
         <v>115</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="4">
         <v>1001</v>
@@ -2716,24 +2719,24 @@
         <v>1650</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M19" s="4">
         <v>140</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="4">
         <v>1001</v>
@@ -2791,24 +2794,24 @@
         <v>1100</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M20" s="4">
         <v>90</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="4">
         <v>1001</v>
@@ -2866,24 +2869,24 @@
         <v>1350</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M21" s="4">
         <v>110</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="4">
         <v>1001</v>
@@ -2941,24 +2944,24 @@
         <v>1650</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M22" s="4">
         <v>135</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P22" s="4">
         <v>1001</v>
@@ -3016,24 +3019,24 @@
         <v>2000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M23" s="4">
         <v>165</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P23" s="4">
         <v>1001</v>
@@ -3091,24 +3094,24 @@
         <v>1350</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M24" s="4">
         <v>95</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P24" s="4">
         <v>1001</v>
@@ -3166,24 +3169,24 @@
         <v>1650</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M25" s="4">
         <v>115</v>
       </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P25" s="4">
         <v>1001</v>
@@ -3241,24 +3244,24 @@
         <v>2000</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M26" s="4">
         <v>145</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P26" s="4">
         <v>1001</v>
@@ -3316,24 +3319,24 @@
         <v>2400</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>52</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M27" s="4">
         <v>180</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P27" s="4">
         <v>1001</v>
